--- a/additional Files/web-with-googlesheet.xlsx
+++ b/additional Files/web-with-googlesheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\pro\GitHub\GitHub\ePiber\additional Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6DAF71C-D87D-4EB6-871C-F064DA0E68DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7652E09-5C49-4ED5-B5AB-7B643969B2B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Personen" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="194">
   <si>
     <t>ID</t>
   </si>
@@ -254,15 +254,6 @@
     <t>Gewinner</t>
   </si>
   <si>
-    <t>260423-1300</t>
-  </si>
-  <si>
-    <t>2-6/3-6/5-7(8)</t>
-  </si>
-  <si>
-    <t>4-6/6-4/5-7(13)</t>
-  </si>
-  <si>
     <t>ZeitpunktMatch</t>
   </si>
   <si>
@@ -272,21 +263,9 @@
     <t>status</t>
   </si>
   <si>
-    <t>260430-1300</t>
-  </si>
-  <si>
-    <t>260424-1230</t>
-  </si>
-  <si>
     <t>offen</t>
   </si>
   <si>
-    <t>260430-1400</t>
-  </si>
-  <si>
-    <t>260424-1000</t>
-  </si>
-  <si>
     <t>Bezeichnung</t>
   </si>
   <si>
@@ -605,22 +584,31 @@
     <t>RausgehangenGrund</t>
   </si>
   <si>
-    <t>260415-1300</t>
-  </si>
-  <si>
-    <t>260505-1900</t>
-  </si>
-  <si>
-    <t>2-6/6-3/5-7(12)</t>
-  </si>
-  <si>
-    <t>260505-1707</t>
-  </si>
-  <si>
-    <t>260506-0944</t>
-  </si>
-  <si>
-    <t>260506-2000</t>
+    <t>260518-1700</t>
+  </si>
+  <si>
+    <t>6-2/6-3</t>
+  </si>
+  <si>
+    <t>260510-0800</t>
+  </si>
+  <si>
+    <t>5-7/6-3/6-4</t>
+  </si>
+  <si>
+    <t>260517-1000</t>
+  </si>
+  <si>
+    <t>4-6/1-6</t>
+  </si>
+  <si>
+    <t>260510-0900</t>
+  </si>
+  <si>
+    <t>260501-1645</t>
+  </si>
+  <si>
+    <t>Kruiß</t>
   </si>
 </sst>
 </file>
@@ -689,7 +677,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -699,6 +687,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -997,7 +986,7 @@
         <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="F2" t="s">
         <v>16</v>
@@ -1017,7 +1006,7 @@
         <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
@@ -1031,7 +1020,7 @@
         <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
@@ -1045,7 +1034,7 @@
         <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
@@ -1059,7 +1048,7 @@
         <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
@@ -1073,7 +1062,7 @@
         <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
@@ -1087,7 +1076,7 @@
         <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
@@ -1098,10 +1087,10 @@
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="D9" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
@@ -1115,7 +1104,7 @@
         <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
@@ -1129,7 +1118,7 @@
         <v>53</v>
       </c>
       <c r="D11" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="K11" t="s">
         <v>33</v>
@@ -1149,7 +1138,7 @@
         <v>35</v>
       </c>
       <c r="D12" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
@@ -1160,10 +1149,10 @@
         <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="D13" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
@@ -1177,7 +1166,7 @@
         <v>38</v>
       </c>
       <c r="D14" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="K14" t="s">
         <v>17</v>
@@ -1197,7 +1186,7 @@
         <v>41</v>
       </c>
       <c r="D15" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="K15" t="s">
         <v>43</v>
@@ -1217,7 +1206,7 @@
         <v>45</v>
       </c>
       <c r="D16" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="K16" t="s">
         <v>47</v>
@@ -1237,7 +1226,7 @@
         <v>49</v>
       </c>
       <c r="D17" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="K17" t="s">
         <v>51</v>
@@ -1257,7 +1246,7 @@
         <v>53</v>
       </c>
       <c r="D18" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="K18" t="s">
         <v>55</v>
@@ -1277,7 +1266,7 @@
         <v>56</v>
       </c>
       <c r="D19" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="K19" t="s">
         <v>58</v>
@@ -1297,7 +1286,7 @@
         <v>15</v>
       </c>
       <c r="D20" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="K20" t="s">
         <v>33</v>
@@ -1311,13 +1300,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="C21" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="D21" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="22" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
@@ -1331,13 +1320,13 @@
         <v>18</v>
       </c>
       <c r="D22" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="F22" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="K22" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
     </row>
     <row r="23" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
@@ -1345,16 +1334,16 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="C23" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D23" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="F23" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="K23" t="s">
         <v>17</v>
@@ -1365,19 +1354,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C24" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D24" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="F24" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="K24" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
     </row>
     <row r="25" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
@@ -1391,10 +1380,10 @@
         <v>30</v>
       </c>
       <c r="D25" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="F25" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="K25" t="s">
         <v>17</v>
@@ -1405,13 +1394,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="C26" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="D26" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="27" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
@@ -1419,13 +1408,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="C27" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="D27" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="28" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
@@ -1433,13 +1422,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="C28" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="D28" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="29" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
@@ -1447,13 +1436,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C29" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="D29" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="30" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
@@ -1461,13 +1450,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="C30" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="D30" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="31" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
@@ -1475,13 +1464,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C31" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="D31" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="32" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
@@ -1489,13 +1478,13 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C32" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="D32" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1503,13 +1492,13 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C33" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="D33" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1517,13 +1506,13 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="C34" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="D34" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1531,13 +1520,13 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="C35" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="D35" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1545,13 +1534,13 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="C36" t="s">
         <v>30</v>
       </c>
       <c r="D36" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1559,13 +1548,13 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="C37" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="D37" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1573,13 +1562,13 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="C38" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="D38" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1587,13 +1576,13 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="C39" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="D39" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1601,13 +1590,13 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C40" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="D40" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1615,13 +1604,13 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="C41" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D41" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1629,13 +1618,13 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="C42" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D42" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1643,13 +1632,13 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C43" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="D43" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1657,13 +1646,13 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="C44" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D44" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1671,13 +1660,13 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="C45" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="D45" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1685,13 +1674,13 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="C46" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="D46" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1702,10 +1691,10 @@
         <v>28</v>
       </c>
       <c r="C47" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="D47" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1713,13 +1702,13 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C48" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="D48" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1727,13 +1716,13 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="C49" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="D49" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1741,13 +1730,13 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="C50" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="D50" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1755,13 +1744,13 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C51" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="D51" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1769,13 +1758,13 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="C52" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="D52" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1783,13 +1772,13 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="C53" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="D53" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1797,13 +1786,13 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="C54" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="D54" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1811,13 +1800,13 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="C55" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="D55" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1825,13 +1814,13 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="C56" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D56" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1839,13 +1828,13 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="C57" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D57" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1853,13 +1842,13 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="C58" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D58" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1867,13 +1856,13 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C59" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D59" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1881,16 +1870,29 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C60" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="D60" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" ht="12.75" x14ac:dyDescent="0.2"/>
+        <v>113</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>113</v>
+      </c>
+    </row>
     <row r="62" spans="1:4" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="63" spans="1:4" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="64" spans="1:4" ht="12.75" x14ac:dyDescent="0.2"/>
@@ -14091,7 +14093,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="5" max="5" width="16.28515625" bestFit="1" customWidth="1"/>
@@ -14113,13 +14115,13 @@
         <v>64</v>
       </c>
       <c r="E1" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="F1" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="G1" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
@@ -14604,6 +14606,17 @@
       </c>
       <c r="C45">
         <v>59</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>2</v>
+      </c>
+      <c r="B46">
+        <v>41</v>
+      </c>
+      <c r="C46">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -14669,19 +14682,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>185</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="J2" t="s">
-        <v>76</v>
+        <v>186</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
@@ -14689,19 +14705,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>192</v>
+        <v>187</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="J3" t="s">
-        <v>77</v>
+        <v>188</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
@@ -14709,19 +14728,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>193</v>
+        <v>189</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="H4">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="J4" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="M4">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="12.75" x14ac:dyDescent="0.2"/>
@@ -14749,7 +14771,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.140625" customWidth="1"/>
@@ -14760,15 +14782,15 @@
     <col min="10" max="10" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D1" t="s">
         <v>61</v>
@@ -14789,112 +14811,46 @@
         <v>71</v>
       </c>
       <c r="J1" t="s">
-        <v>80</v>
-      </c>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>191</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
+        <v>192</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="H2">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="J2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C3" t="s">
-        <v>85</v>
-      </c>
-      <c r="F3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>14</v>
-      </c>
-      <c r="J3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="C4" t="s">
-        <v>195</v>
-      </c>
-      <c r="F4">
-        <v>22</v>
-      </c>
-      <c r="H4">
-        <v>24</v>
-      </c>
-      <c r="J4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="C5" t="s">
-        <v>196</v>
-      </c>
-      <c r="F5">
-        <v>20</v>
-      </c>
-      <c r="H5">
-        <v>21</v>
-      </c>
-      <c r="J5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="C6" t="s">
-        <v>197</v>
-      </c>
-      <c r="F6">
-        <v>38</v>
-      </c>
-      <c r="H6">
-        <v>39</v>
-      </c>
-      <c r="J6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="8" spans="1:12" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="9" spans="1:12" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="10" spans="1:12" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="11" spans="1:12" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="12" spans="1:12" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="13" spans="1:12" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="14" spans="1:12" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="15" spans="1:12" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="16" spans="1:12" ht="12.75" x14ac:dyDescent="0.2"/>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="1:10" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:10" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="6" spans="1:10" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="7" spans="1:10" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="8" spans="1:10" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="9" spans="1:10" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="10" spans="1:10" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="11" spans="1:10" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="12" spans="1:10" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="13" spans="1:10" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="14" spans="1:10" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="15" spans="1:10" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="16" spans="1:10" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="17" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="18" ht="12.75" x14ac:dyDescent="0.2"/>
   </sheetData>
@@ -14918,19 +14874,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -14938,19 +14894,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="D2" s="3">
         <v>2</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -14958,19 +14914,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="D3" s="3">
         <v>2</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -14978,19 +14934,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D4" s="3">
         <v>2</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -14998,19 +14954,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D5" s="3">
         <v>2</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -15036,16 +14992,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>64</v>
@@ -15056,7 +15012,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C2" s="3">
         <v>1</v>
@@ -15072,7 +15028,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C3" s="3">
         <v>1</v>
@@ -15088,7 +15044,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="3">
@@ -15104,7 +15060,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="3">
@@ -15136,22 +15092,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -15162,7 +15118,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -15177,7 +15133,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -15194,7 +15150,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -15211,7 +15167,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -15228,11 +15184,11 @@
         <v>4</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="F6" s="3">
         <v>20260701</v>
@@ -15260,7 +15216,7 @@
         <v>63</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
